--- a/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
+++ b/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1350</v>
+        <v>1800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4650</v>
+        <v>4200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1150,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>46129</v>
+      </c>
+      <c r="C12" s="4">
+        <v>150</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1176,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>46153</v>
+      </c>
+      <c r="C13" s="4">
+        <v>150</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1202,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C14" s="4">
+        <v>150</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>

--- a/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
+++ b/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1246,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>46176</v>
+      </c>
+      <c r="C15" s="4">
+        <v>150</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
+++ b/LoanOfficer-A/2026/170 salam bidyalaxmi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4050</v>
+        <v>3750</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1278,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C16" s="4">
+        <v>150</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1304,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>46179</v>
+      </c>
+      <c r="C17" s="4">
+        <v>150</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
